--- a/dcf/NVS.xlsx
+++ b/dcf/NVS.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1099,25 +1099,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.04824305710607656</v>
+        <v>0.04817973085413062</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.05324305710607655</v>
+        <v>0.05317973085413061</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.05824305710607656</v>
+        <v>0.05817973085413062</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.06324305710607656</v>
+        <v>0.06317973085413062</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.06824305710607656</v>
+        <v>0.06817973085413062</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.07324305710607655</v>
+        <v>0.07317973085413061</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.07824305710607656</v>
+        <v>0.07817973085413062</v>
       </c>
     </row>
     <row r="5">
@@ -1125,25 +1125,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>227.4984462063315</v>
+        <v>227.6187514119854</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>218.2286611213689</v>
+        <v>218.343287921847</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>209.3950429219411</v>
+        <v>209.5042929607756</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>200.9744841542988</v>
+        <v>201.0786415240428</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>192.9452184900781</v>
+        <v>193.0445508360429</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>185.2867365901008</v>
+        <v>185.3814961396987</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>177.9797076253957</v>
+        <v>178.0701321484387</v>
       </c>
     </row>
     <row r="6">
@@ -1151,25 +1151,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>243.4808609338565</v>
+        <v>243.6108246131211</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>233.4683567132307</v>
+        <v>233.59214941336</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>223.9298095627616</v>
+        <v>224.0477602049029</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>214.8400241230884</v>
+        <v>214.9524424485029</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>206.1752705552584</v>
+        <v>206.2824483333322</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>197.9131924596498</v>
+        <v>198.0154046143903</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>190.0327209933063</v>
+        <v>190.1302266541923</v>
       </c>
     </row>
     <row r="7">
@@ -1177,25 +1177,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>259.4632756613815</v>
+        <v>259.6028978142568</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>248.7080523050926</v>
+        <v>248.8410109048731</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>238.4645762035821</v>
+        <v>238.5912274490302</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>228.7055640918781</v>
+        <v>228.826243372963</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>219.4053226204388</v>
+        <v>219.5203458306216</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>210.5396483291989</v>
+        <v>210.649313089082</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>202.0857343612168</v>
+        <v>202.190321159946</v>
       </c>
     </row>
     <row r="8">
@@ -1203,25 +1203,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>275.4456903889064</v>
+        <v>275.5949710153924</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>263.9477478969545</v>
+        <v>264.0898723963861</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>252.9993428444027</v>
+        <v>253.1346946931575</v>
       </c>
       <c r="E8" s="53" t="n">
-        <v>242.5711040606677</v>
+        <v>242.7000442974231</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>232.6353746856192</v>
+        <v>232.7582433279109</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>223.166104198748</v>
+        <v>223.2832215637736</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>214.1387477291273</v>
+        <v>214.2504156656996</v>
       </c>
     </row>
     <row r="9">
@@ -1229,25 +1229,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>291.4281051164314</v>
+        <v>291.5870442165282</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>279.1874434888163</v>
+        <v>279.3387338878991</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>267.5341094852233</v>
+        <v>267.6781619372848</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>256.4366440294573</v>
+        <v>256.5738452218832</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>245.8654267507997</v>
+        <v>245.9961408252002</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>235.7925600682971</v>
+        <v>235.9171300384652</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>226.1917610970378</v>
+        <v>226.3105101714532</v>
       </c>
     </row>
     <row r="10">
@@ -1255,25 +1255,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>307.4105198439563</v>
+        <v>307.5791174176638</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>294.4271390806782</v>
+        <v>294.5875953794122</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>282.0688761260438</v>
+        <v>282.2216291814121</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>270.3021839982469</v>
+        <v>270.4476461463433</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>259.09547881598</v>
+        <v>259.2340383224895</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>248.4190159378463</v>
+        <v>248.5510385131568</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>238.2447744649484</v>
+        <v>238.3706046772068</v>
       </c>
     </row>
     <row r="11">
@@ -1281,25 +1281,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>323.3929345714813</v>
+        <v>323.5711906187996</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>309.66683467254</v>
+        <v>309.8364568709252</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>296.6036427668644</v>
+        <v>296.7650964255394</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>284.1677239670366</v>
+        <v>284.3214470708035</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>272.3255308811604</v>
+        <v>272.4719358197788</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>261.0454718073953</v>
+        <v>261.1849469878484</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>250.2977878328589</v>
+        <v>250.4306991829604</v>
       </c>
     </row>
     <row r="13">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="B13" s="54" t="n">
-        <v>159.8999938964844</v>
+        <v>156.7550048828125</v>
       </c>
     </row>
     <row r="14">
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.06324305710607656</v>
+        <v>0.06317973085413062</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1665,7 +1665,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>1.024346564281452</v>
+        <v>1.024334954758462</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>159.8999938964844</v>
+        <v>156.7550048828125</v>
       </c>
     </row>
     <row r="49">
@@ -24566,13 +24566,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>242.5711040606677</v>
+        <v>242.7000442974231</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>335.4229686582059</v>
+        <v>335.6038270166883</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>172.4474634558207</v>
+        <v>172.5376496818828</v>
       </c>
     </row>
     <row r="59">
